--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9420"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14460" windowHeight="7250"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,38 +21,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+  <si>
+    <t>产品主代码*</t>
+  </si>
+  <si>
+    <t>开放期起始日*</t>
+  </si>
+  <si>
+    <t>开放期结束日（YYYY-MM-DD)*</t>
+  </si>
+  <si>
+    <t>产品冷静期（YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>运作起始日（YYYY-MM-DD)*</t>
+  </si>
+  <si>
+    <t>自动赎回日（YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>客户实际持有天数</t>
+  </si>
   <si>
     <t>产品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>产品主代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>开放起始日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>开放结束日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品冷静期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>运作起始日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>自动赎回日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>实际持有天数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -123,17 +130,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,46 +441,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.90625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.08984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" customWidth="1"/>
-    <col min="8" max="8" width="13.36328125" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" customWidth="1"/>
+    <col min="3" max="3" width="26.7265625" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" customWidth="1"/>
+    <col min="5" max="5" width="24.90625" customWidth="1"/>
+    <col min="6" max="6" width="23.453125" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -491,12 +485,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A2:A8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.36328125" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A0A913-C484-4358-8771-E58594B30932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14460" windowHeight="7250"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -78,11 +79,13 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -130,12 +133,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,36 +449,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.08984375" customWidth="1"/>
-    <col min="3" max="3" width="26.7265625" customWidth="1"/>
-    <col min="4" max="4" width="27.81640625" customWidth="1"/>
-    <col min="5" max="5" width="24.90625" customWidth="1"/>
-    <col min="6" max="6" width="23.453125" customWidth="1"/>
-    <col min="7" max="7" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -484,11 +493,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.36328125" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -534,9 +543,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A0A913-C484-4358-8771-E58594B30932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,18 +29,6 @@
     <t>开放期起始日*</t>
   </si>
   <si>
-    <t>开放期结束日（YYYY-MM-DD)*</t>
-  </si>
-  <si>
-    <t>产品冷静期（YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>运作起始日（YYYY-MM-DD)*</t>
-  </si>
-  <si>
-    <t>自动赎回日（YYYY-MM-DD)</t>
-  </si>
-  <si>
     <t>客户实际持有天数</t>
   </si>
   <si>
@@ -61,12 +48,28 @@
   </si>
   <si>
     <t>自动赎回日</t>
+  </si>
+  <si>
+    <t>开放期结束日（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品冷静期（YYYY/MM/DD)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>运作起始日（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动赎回日（YYYY/MM/DD)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -449,20 +452,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.77734375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="16.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="13.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,19 +473,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -493,46 +496,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -543,9 +546,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
@@ -143,10 +143,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23250" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,19 +50,19 @@
     <t>自动赎回日</t>
   </si>
   <si>
-    <t>开放期结束日（YYYY/MM/DD)*</t>
+    <t>开放期结束日（YYYY-MM-DD)*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>产品冷静期（YYYY/MM/DD)</t>
+    <t>产品冷静期（YYYY-MM-DD)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>运作起始日（YYYY/MM/DD)*</t>
+    <t>运作起始日（YYYY-MM-DD)*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>自动赎回日（YYYY/MM/DD)</t>
+    <t>自动赎回日（YYYY-MM-DD)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -143,10 +143,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,18 +454,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="16.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.7265625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.7265625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.90625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.453125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,42 +498,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="1" max="1" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -548,7 +548,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,19 +50,19 @@
     <t>自动赎回日</t>
   </si>
   <si>
-    <t>开放期结束日（YYYY-MM-DD)*</t>
+    <t>开放期结束日（YYYY/MM/DD)*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>产品冷静期（YYYY-MM-DD)</t>
+    <t>产品冷静期（YYYY/MM/DD)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>运作起始日（YYYY-MM-DD)*</t>
+    <t>运作起始日（YYYY/MM/DD)*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>自动赎回日（YYYY-MM-DD)</t>
+    <t>自动赎回日（YYYY/MM/DD)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -143,10 +143,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,18 +454,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.453125" customWidth="1"/>
-    <col min="2" max="2" width="16.08984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.7265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.7265625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.90625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.453125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="16.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="13.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,42 +498,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.36328125" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -548,7 +548,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
